--- a/exercise/Admin/Admin Hotel/Tes Excel Admin Hotel 1.xlsx
+++ b/exercise/Admin/Admin Hotel/Tes Excel Admin Hotel 1.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24729"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Documents\Buat Youtube\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Pemrograman\Excel\excel\exercise\Admin\Admin Hotel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1496CFB9-63C2-4443-A1E4-F0C6ACFAE173}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{730D9222-B557-43E0-9362-31BF33CE6212}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="11070" tabRatio="599" xr2:uid="{3FDB169C-B558-497A-A591-5CB360CCCFEA}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11310" tabRatio="599" xr2:uid="{3FDB169C-B558-497A-A591-5CB360CCCFEA}"/>
   </bookViews>
   <sheets>
     <sheet name="Soal" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -23,7 +23,9 @@
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
@@ -469,7 +471,7 @@
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="41" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
@@ -484,7 +486,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -492,22 +493,22 @@
     <xf numFmtId="41" fontId="4" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="41" fontId="4" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="41" fontId="4" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -548,7 +549,14 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="41" fontId="4" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -571,13 +579,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="3" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -926,366 +927,444 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:15" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="36" t="s">
+      <c r="B1" s="38" t="s">
         <v>48</v>
       </c>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
-      <c r="H1" s="36"/>
-      <c r="I1" s="36"/>
-      <c r="J1" s="36"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="38"/>
+      <c r="J1" s="38"/>
     </row>
     <row r="2" spans="2:15" s="7" customFormat="1" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="23" t="s">
+      <c r="B2" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="24" t="s">
+      <c r="C2" s="23" t="s">
         <v>50</v>
       </c>
-      <c r="D2" s="23" t="s">
+      <c r="D2" s="22" t="s">
         <v>49</v>
       </c>
-      <c r="E2" s="24" t="s">
+      <c r="E2" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="23" t="s">
+      <c r="F2" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="23" t="s">
+      <c r="G2" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="H2" s="23" t="s">
+      <c r="H2" s="22" t="s">
         <v>52</v>
       </c>
-      <c r="I2" s="23" t="s">
+      <c r="I2" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="J2" s="23" t="s">
+      <c r="J2" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="L2" s="43" t="s">
+      <c r="L2" s="45" t="s">
         <v>28</v>
       </c>
-      <c r="M2" s="43"/>
-      <c r="N2" s="43"/>
+      <c r="M2" s="45"/>
+      <c r="N2" s="45"/>
     </row>
     <row r="3" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B3" s="25" t="s">
+      <c r="B3" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="26" t="s">
+      <c r="C3" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="D3" s="27"/>
-      <c r="E3" s="28"/>
-      <c r="F3" s="33"/>
-      <c r="G3" s="29"/>
-      <c r="H3" s="33"/>
-      <c r="I3" s="34"/>
-      <c r="J3" s="35"/>
+      <c r="D3" s="26" t="str">
+        <f>VLOOKUP(LEFT(C3,1),$L$3:$N$8,2,FALSE)</f>
+        <v>President</v>
+      </c>
+      <c r="E3" s="27" t="str">
+        <f>HLOOKUP(RIGHT(C3,2),$L$10:$O$12,2,FALSE)</f>
+        <v>Single</v>
+      </c>
+      <c r="F3" s="27"/>
+      <c r="G3" s="28"/>
+      <c r="H3" s="32"/>
+      <c r="I3" s="33"/>
+      <c r="J3" s="34"/>
       <c r="K3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="L3" s="38" t="s">
+      <c r="L3" s="40" t="s">
         <v>32</v>
       </c>
-      <c r="M3" s="40" t="s">
+      <c r="M3" s="42" t="s">
         <v>49</v>
       </c>
-      <c r="N3" s="38" t="s">
+      <c r="N3" s="40" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="4" spans="2:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="25" t="s">
+      <c r="B4" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="30" t="s">
+      <c r="C4" s="29" t="s">
         <v>39</v>
       </c>
-      <c r="D4" s="27"/>
-      <c r="E4" s="28"/>
-      <c r="F4" s="33"/>
-      <c r="G4" s="29"/>
-      <c r="H4" s="33"/>
-      <c r="I4" s="34"/>
-      <c r="J4" s="35"/>
-      <c r="L4" s="39"/>
-      <c r="M4" s="41"/>
-      <c r="N4" s="39"/>
+      <c r="D4" s="26" t="str">
+        <f t="shared" ref="D4:D15" si="0">VLOOKUP(LEFT(C4,1),$L$3:$N$8,2,FALSE)</f>
+        <v>President</v>
+      </c>
+      <c r="E4" s="27" t="str">
+        <f t="shared" ref="E4:E15" si="1">HLOOKUP(RIGHT(C4,2),$L$10:$O$12,2,FALSE)</f>
+        <v>Double</v>
+      </c>
+      <c r="F4" s="27"/>
+      <c r="G4" s="28"/>
+      <c r="H4" s="32"/>
+      <c r="I4" s="33"/>
+      <c r="J4" s="34"/>
+      <c r="L4" s="41"/>
+      <c r="M4" s="43"/>
+      <c r="N4" s="41"/>
     </row>
     <row r="5" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B5" s="25" t="s">
+      <c r="B5" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="30" t="s">
+      <c r="C5" s="29" t="s">
         <v>40</v>
       </c>
-      <c r="D5" s="27"/>
-      <c r="E5" s="28"/>
-      <c r="F5" s="33"/>
-      <c r="G5" s="29"/>
-      <c r="H5" s="33"/>
-      <c r="I5" s="34"/>
-      <c r="J5" s="35"/>
-      <c r="L5" s="10" t="s">
+      <c r="D5" s="26" t="str">
+        <f t="shared" si="0"/>
+        <v>Business</v>
+      </c>
+      <c r="E5" s="27" t="str">
+        <f t="shared" si="1"/>
+        <v>Family</v>
+      </c>
+      <c r="F5" s="27"/>
+      <c r="G5" s="28"/>
+      <c r="H5" s="32"/>
+      <c r="I5" s="33"/>
+      <c r="J5" s="34"/>
+      <c r="L5" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="M5" s="8" t="s">
+      <c r="M5" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="N5" s="11">
+      <c r="N5" s="10">
         <v>300000</v>
       </c>
     </row>
     <row r="6" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B6" s="31" t="s">
+      <c r="B6" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="30" t="s">
+      <c r="C6" s="29" t="s">
         <v>41</v>
       </c>
-      <c r="D6" s="27"/>
-      <c r="E6" s="28"/>
-      <c r="F6" s="33"/>
-      <c r="G6" s="29"/>
-      <c r="H6" s="33"/>
-      <c r="I6" s="34"/>
-      <c r="J6" s="35"/>
-      <c r="L6" s="10" t="s">
+      <c r="D6" s="26" t="str">
+        <f t="shared" si="0"/>
+        <v>Excecutive</v>
+      </c>
+      <c r="E6" s="27" t="str">
+        <f t="shared" si="1"/>
+        <v>Family</v>
+      </c>
+      <c r="F6" s="27"/>
+      <c r="G6" s="28"/>
+      <c r="H6" s="32"/>
+      <c r="I6" s="33"/>
+      <c r="J6" s="34"/>
+      <c r="L6" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="M6" s="8" t="s">
+      <c r="M6" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="N6" s="11">
+      <c r="N6" s="10">
         <v>500000</v>
       </c>
     </row>
     <row r="7" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B7" s="31" t="s">
+      <c r="B7" s="30" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="30" t="s">
+      <c r="C7" s="29" t="s">
         <v>42</v>
       </c>
-      <c r="D7" s="27"/>
-      <c r="E7" s="28"/>
-      <c r="F7" s="33"/>
-      <c r="G7" s="29"/>
-      <c r="H7" s="33"/>
-      <c r="I7" s="34"/>
-      <c r="J7" s="35"/>
-      <c r="L7" s="10" t="s">
+      <c r="D7" s="26" t="str">
+        <f t="shared" si="0"/>
+        <v>Suite</v>
+      </c>
+      <c r="E7" s="27" t="str">
+        <f t="shared" si="1"/>
+        <v>Double</v>
+      </c>
+      <c r="F7" s="27"/>
+      <c r="G7" s="28"/>
+      <c r="H7" s="32"/>
+      <c r="I7" s="33"/>
+      <c r="J7" s="34"/>
+      <c r="L7" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="M7" s="8" t="s">
+      <c r="M7" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="N7" s="11">
+      <c r="N7" s="10">
         <v>1000000</v>
       </c>
     </row>
     <row r="8" spans="2:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B8" s="31" t="s">
+      <c r="B8" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="30" t="s">
+      <c r="C8" s="29" t="s">
         <v>41</v>
       </c>
-      <c r="D8" s="27"/>
-      <c r="E8" s="28"/>
-      <c r="F8" s="33"/>
-      <c r="G8" s="29"/>
-      <c r="H8" s="33"/>
-      <c r="I8" s="34"/>
-      <c r="J8" s="35"/>
+      <c r="D8" s="26" t="str">
+        <f t="shared" si="0"/>
+        <v>Excecutive</v>
+      </c>
+      <c r="E8" s="27" t="str">
+        <f t="shared" si="1"/>
+        <v>Family</v>
+      </c>
+      <c r="F8" s="27"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="32"/>
+      <c r="I8" s="33"/>
+      <c r="J8" s="34"/>
       <c r="L8" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="M8" s="9" t="s">
+      <c r="M8" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="N8" s="12">
+      <c r="N8" s="11">
         <v>3000000</v>
       </c>
     </row>
     <row r="9" spans="2:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B9" s="31" t="s">
+      <c r="B9" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="30" t="s">
+      <c r="C9" s="29" t="s">
         <v>42</v>
       </c>
-      <c r="D9" s="27"/>
-      <c r="E9" s="28"/>
-      <c r="F9" s="33"/>
-      <c r="G9" s="29"/>
-      <c r="H9" s="33"/>
-      <c r="I9" s="34"/>
-      <c r="J9" s="35"/>
-      <c r="L9" s="42" t="s">
+      <c r="D9" s="26" t="str">
+        <f t="shared" si="0"/>
+        <v>Suite</v>
+      </c>
+      <c r="E9" s="27" t="str">
+        <f t="shared" si="1"/>
+        <v>Double</v>
+      </c>
+      <c r="F9" s="27"/>
+      <c r="G9" s="28"/>
+      <c r="H9" s="32"/>
+      <c r="I9" s="33"/>
+      <c r="J9" s="34"/>
+      <c r="L9" s="44" t="s">
         <v>34</v>
       </c>
-      <c r="M9" s="42"/>
-      <c r="N9" s="42"/>
-      <c r="O9" s="42"/>
+      <c r="M9" s="44"/>
+      <c r="N9" s="44"/>
+      <c r="O9" s="44"/>
     </row>
     <row r="10" spans="2:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B10" s="31" t="s">
+      <c r="B10" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="30" t="s">
+      <c r="C10" s="29" t="s">
         <v>43</v>
       </c>
-      <c r="D10" s="27"/>
-      <c r="E10" s="28"/>
-      <c r="F10" s="33"/>
-      <c r="G10" s="29"/>
-      <c r="H10" s="33"/>
-      <c r="I10" s="34"/>
-      <c r="J10" s="35"/>
+      <c r="D10" s="26" t="str">
+        <f t="shared" si="0"/>
+        <v>President</v>
+      </c>
+      <c r="E10" s="27" t="str">
+        <f t="shared" si="1"/>
+        <v>Family</v>
+      </c>
+      <c r="F10" s="27"/>
+      <c r="G10" s="28"/>
+      <c r="H10" s="32"/>
+      <c r="I10" s="33"/>
+      <c r="J10" s="34"/>
       <c r="L10" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="M10" s="14" t="s">
+      <c r="M10" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="N10" s="15" t="s">
+      <c r="N10" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="O10" s="16" t="s">
+      <c r="O10" s="15" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="11" spans="2:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="31" t="s">
+      <c r="B11" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="30" t="s">
+      <c r="C11" s="29" t="s">
         <v>40</v>
       </c>
-      <c r="D11" s="27"/>
-      <c r="E11" s="28"/>
-      <c r="F11" s="33"/>
-      <c r="G11" s="29"/>
-      <c r="H11" s="33"/>
-      <c r="I11" s="34"/>
-      <c r="J11" s="35"/>
-      <c r="L11" s="13" t="s">
+      <c r="D11" s="26" t="str">
+        <f t="shared" si="0"/>
+        <v>Business</v>
+      </c>
+      <c r="E11" s="27" t="str">
+        <f t="shared" si="1"/>
+        <v>Family</v>
+      </c>
+      <c r="F11" s="27"/>
+      <c r="G11" s="28"/>
+      <c r="H11" s="32"/>
+      <c r="I11" s="33"/>
+      <c r="J11" s="34"/>
+      <c r="L11" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="M11" s="17" t="s">
+      <c r="M11" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="N11" s="18" t="s">
+      <c r="N11" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="O11" s="19" t="s">
+      <c r="O11" s="18" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="12" spans="2:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="31" t="s">
+      <c r="B12" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="30" t="s">
+      <c r="C12" s="29" t="s">
         <v>44</v>
       </c>
-      <c r="D12" s="27"/>
-      <c r="E12" s="28"/>
-      <c r="F12" s="33"/>
-      <c r="G12" s="29"/>
-      <c r="H12" s="33"/>
-      <c r="I12" s="34"/>
-      <c r="J12" s="35"/>
-      <c r="L12" s="32" t="s">
+      <c r="D12" s="26" t="str">
+        <f t="shared" si="0"/>
+        <v>Excecutive</v>
+      </c>
+      <c r="E12" s="27" t="str">
+        <f t="shared" si="1"/>
+        <v>Double</v>
+      </c>
+      <c r="F12" s="27"/>
+      <c r="G12" s="28"/>
+      <c r="H12" s="32"/>
+      <c r="I12" s="33"/>
+      <c r="J12" s="34"/>
+      <c r="L12" s="31" t="s">
         <v>53</v>
       </c>
-      <c r="M12" s="20">
+      <c r="M12" s="19">
         <v>100000</v>
       </c>
-      <c r="N12" s="21">
+      <c r="N12" s="20">
         <v>200000</v>
       </c>
-      <c r="O12" s="22">
+      <c r="O12" s="21">
         <v>300000</v>
       </c>
     </row>
     <row r="13" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B13" s="31" t="s">
+      <c r="B13" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="30" t="s">
+      <c r="C13" s="29" t="s">
         <v>42</v>
       </c>
-      <c r="D13" s="27"/>
-      <c r="E13" s="28"/>
-      <c r="F13" s="33"/>
-      <c r="G13" s="29"/>
-      <c r="H13" s="33"/>
-      <c r="I13" s="34"/>
-      <c r="J13" s="35"/>
+      <c r="D13" s="26" t="str">
+        <f t="shared" si="0"/>
+        <v>Suite</v>
+      </c>
+      <c r="E13" s="27" t="str">
+        <f t="shared" si="1"/>
+        <v>Double</v>
+      </c>
+      <c r="F13" s="27"/>
+      <c r="G13" s="28"/>
+      <c r="H13" s="32"/>
+      <c r="I13" s="33"/>
+      <c r="J13" s="34"/>
       <c r="L13" s="1" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="14" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B14" s="25" t="s">
+      <c r="B14" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="C14" s="30" t="s">
+      <c r="C14" s="29" t="s">
         <v>41</v>
       </c>
-      <c r="D14" s="27"/>
-      <c r="E14" s="28"/>
-      <c r="F14" s="33"/>
-      <c r="G14" s="29"/>
-      <c r="H14" s="33"/>
-      <c r="I14" s="34"/>
-      <c r="J14" s="35"/>
-      <c r="L14" s="37" t="s">
+      <c r="D14" s="26" t="str">
+        <f t="shared" si="0"/>
+        <v>Excecutive</v>
+      </c>
+      <c r="E14" s="27" t="str">
+        <f t="shared" si="1"/>
+        <v>Family</v>
+      </c>
+      <c r="F14" s="27"/>
+      <c r="G14" s="28"/>
+      <c r="H14" s="32"/>
+      <c r="I14" s="33"/>
+      <c r="J14" s="34"/>
+      <c r="L14" s="39" t="s">
         <v>47</v>
       </c>
-      <c r="M14" s="37"/>
-      <c r="N14" s="37"/>
-      <c r="O14" s="37"/>
+      <c r="M14" s="39"/>
+      <c r="N14" s="39"/>
+      <c r="O14" s="39"/>
     </row>
     <row r="15" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B15" s="25" t="s">
+      <c r="B15" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="30" t="s">
+      <c r="C15" s="29" t="s">
         <v>38</v>
       </c>
-      <c r="D15" s="27"/>
-      <c r="E15" s="28"/>
-      <c r="F15" s="33"/>
-      <c r="G15" s="29"/>
-      <c r="H15" s="33"/>
-      <c r="I15" s="34"/>
-      <c r="J15" s="35"/>
-      <c r="L15" s="37"/>
-      <c r="M15" s="37"/>
-      <c r="N15" s="37"/>
-      <c r="O15" s="37"/>
+      <c r="D15" s="26" t="str">
+        <f t="shared" si="0"/>
+        <v>Suite</v>
+      </c>
+      <c r="E15" s="27" t="str">
+        <f t="shared" si="1"/>
+        <v>Single</v>
+      </c>
+      <c r="F15" s="27"/>
+      <c r="G15" s="28"/>
+      <c r="H15" s="32"/>
+      <c r="I15" s="33"/>
+      <c r="J15" s="34"/>
+      <c r="L15" s="39"/>
+      <c r="M15" s="39"/>
+      <c r="N15" s="39"/>
+      <c r="O15" s="39"/>
     </row>
     <row r="17" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B17" s="44" t="s">
+      <c r="B17" s="35" t="s">
         <v>54</v>
       </c>
-      <c r="D17" s="46" t="s">
+      <c r="D17" s="36" t="s">
         <v>55</v>
       </c>
-      <c r="E17" s="45"/>
-      <c r="F17" s="45"/>
-      <c r="G17" s="45"/>
-      <c r="H17" s="45"/>
-      <c r="I17" s="45"/>
-      <c r="J17" s="45"/>
+      <c r="E17" s="37"/>
+      <c r="F17" s="37"/>
+      <c r="G17" s="37"/>
+      <c r="H17" s="37"/>
+      <c r="I17" s="37"/>
+      <c r="J17" s="37"/>
     </row>
     <row r="28" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C28" s="1"/>
